--- a/test-data/smoke_test.xlsx
+++ b/test-data/smoke_test.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="36">
   <si>
     <t>scenario</t>
   </si>
@@ -72,17 +72,74 @@
     <t>Customer gagal memilih charger station karena status charger station offline</t>
   </si>
   <si>
-    <t>Pilih Charger</t>
-  </si>
-  <si>
     <t>LOG001</t>
+  </si>
+  <si>
+    <t>voucherCode</t>
+  </si>
+  <si>
+    <t>inputKWh</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>ODR002</t>
+  </si>
+  <si>
+    <t>Customer berhasil melakukan pemesanan EV Charging dengan metode Pembayaran</t>
+  </si>
+  <si>
+    <t>Customer berhasil melakukan pemesanan EV Charging dengan submit kode Voucher</t>
+  </si>
+  <si>
+    <t>ODR003</t>
+  </si>
+  <si>
+    <t>ODR004</t>
+  </si>
+  <si>
+    <t>Customer gagal melakukan pemesanan EV Charging karena kode voucher invalid</t>
+  </si>
+  <si>
+    <t>0895385252785</t>
+  </si>
+  <si>
+    <t>EVRZUH</t>
+  </si>
+  <si>
+    <t>EVCSKU</t>
+  </si>
+  <si>
+    <t>Select Charger &amp; Connector</t>
+  </si>
+  <si>
+    <t>Confirm Payment &amp; Submit Order</t>
+  </si>
+  <si>
+    <t>Ipyevcs01!@</t>
+  </si>
+  <si>
+    <t>ODR005</t>
+  </si>
+  <si>
+    <t>Customer gagal melakukan pemesanan EV Charging karena kode voucher sudah kedaluarsa</t>
+  </si>
+  <si>
+    <t>Customer gagal melakukan pemesanan EV Charging karena tidak ada metode pembayaran yang terdaftar</t>
+  </si>
+  <si>
+    <t>ODR006</t>
+  </si>
+  <si>
+    <t>EVNVWZ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,14 +163,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -190,7 +239,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -219,44 +268,31 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -540,182 +576,253 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" style="19" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="99.7109375" style="23" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="19" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" style="19" customWidth="1"/>
-    <col min="8" max="16384" width="8.7109375" style="19"/>
+    <col min="1" max="1" width="9.42578125" style="16" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="9" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="99.7109375" style="18" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="16" customWidth="1"/>
+    <col min="7" max="7" width="31.7109375" style="16" customWidth="1"/>
+    <col min="8" max="9" width="16.28515625" style="16" customWidth="1"/>
+    <col min="10" max="16384" width="8.7109375" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="14" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="H1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="I1" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="20" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-    </row>
-    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-    </row>
-    <row r="6" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-    </row>
-    <row r="7" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-    </row>
-    <row r="8" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-    </row>
-    <row r="9" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-    </row>
-    <row r="10" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-    </row>
-    <row r="11" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-    </row>
-    <row r="12" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="G3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="12"/>
+    </row>
+    <row r="6" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2" display="testing.b2c.001@gmail.com"/>
-    <hyperlink ref="E2" r:id="rId3" display="testing.b2c.001@gmail.com"/>
-    <hyperlink ref="F2" r:id="rId4"/>
+    <hyperlink ref="E2" r:id="rId1" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F4" r:id="rId4"/>
+    <hyperlink ref="E3" r:id="rId5" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F3" r:id="rId6"/>
+    <hyperlink ref="E5" r:id="rId7" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F5" r:id="rId8"/>
+    <hyperlink ref="E6" r:id="rId9" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F6" r:id="rId10"/>
+    <hyperlink ref="E8" r:id="rId11" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F8" r:id="rId12"/>
+    <hyperlink ref="E7" r:id="rId13" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F7" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" customWidth="1"/>
@@ -728,7 +835,7 @@
     <col min="8" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>8</v>
       </c>
@@ -738,7 +845,7 @@
       <c r="C1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="9" t="s">
@@ -750,96 +857,193 @@
       <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="H1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="1:9" s="16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" s="16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" s="16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="12"/>
+    </row>
+    <row r="6" spans="1:9" s="16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="D7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:9" s="16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F8" s="15" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
@@ -848,7 +1052,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
@@ -857,7 +1061,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
@@ -870,10 +1074,20 @@
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="testing.b2c.001@gmail.com"/>
     <hyperlink ref="F2" r:id="rId2"/>
-    <hyperlink ref="E3" r:id="rId3" display="testing.b2c.001@gmail.com"/>
-    <hyperlink ref="F3" r:id="rId4"/>
+    <hyperlink ref="E4" r:id="rId3" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F4" r:id="rId4"/>
+    <hyperlink ref="E3" r:id="rId5" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F3" r:id="rId6"/>
+    <hyperlink ref="E5" r:id="rId7" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F5" r:id="rId8"/>
+    <hyperlink ref="E6" r:id="rId9" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F6" r:id="rId10"/>
+    <hyperlink ref="E8" r:id="rId11" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F8" r:id="rId12"/>
+    <hyperlink ref="E7" r:id="rId13" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F7" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
--- a/test-data/smoke_test.xlsx
+++ b/test-data/smoke_test.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="36">
   <si>
     <t>scenario</t>
   </si>
@@ -576,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="16" customWidth="1"/>
@@ -621,180 +621,28 @@
     </row>
     <row r="2" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="12"/>
+        <v>25</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-    </row>
-    <row r="3" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-    </row>
-    <row r="4" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="12"/>
-    </row>
-    <row r="5" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="12"/>
-    </row>
-    <row r="6" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>18</v>
       </c>
     </row>
@@ -802,21 +650,9 @@
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="testing.b2c.001@gmail.com"/>
     <hyperlink ref="F2" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3" display="testing.b2c.001@gmail.com"/>
-    <hyperlink ref="F4" r:id="rId4"/>
-    <hyperlink ref="E3" r:id="rId5" display="testing.b2c.001@gmail.com"/>
-    <hyperlink ref="F3" r:id="rId6"/>
-    <hyperlink ref="E5" r:id="rId7" display="testing.b2c.001@gmail.com"/>
-    <hyperlink ref="F5" r:id="rId8"/>
-    <hyperlink ref="E6" r:id="rId9" display="testing.b2c.001@gmail.com"/>
-    <hyperlink ref="F6" r:id="rId10"/>
-    <hyperlink ref="E8" r:id="rId11" display="testing.b2c.001@gmail.com"/>
-    <hyperlink ref="F8" r:id="rId12"/>
-    <hyperlink ref="E7" r:id="rId13" display="testing.b2c.001@gmail.com"/>
-    <hyperlink ref="F7" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId15"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/test-data/smoke_test.xlsx
+++ b/test-data/smoke_test.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="36">
   <si>
     <t>scenario</t>
   </si>
@@ -576,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="16" customWidth="1"/>
@@ -621,28 +621,180 @@
     </row>
     <row r="2" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="12"/>
+    </row>
+    <row r="6" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12" t="s">
+      <c r="H6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12" t="s">
         <v>18</v>
       </c>
     </row>
@@ -650,9 +802,21 @@
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="testing.b2c.001@gmail.com"/>
     <hyperlink ref="F2" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F4" r:id="rId4"/>
+    <hyperlink ref="E3" r:id="rId5" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F3" r:id="rId6"/>
+    <hyperlink ref="E5" r:id="rId7" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F5" r:id="rId8"/>
+    <hyperlink ref="E6" r:id="rId9" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F6" r:id="rId10"/>
+    <hyperlink ref="E8" r:id="rId11" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F8" r:id="rId12"/>
+    <hyperlink ref="E7" r:id="rId13" display="testing.b2c.001@gmail.com"/>
+    <hyperlink ref="F7" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
 
